--- a/artfynd/A 8596-2022 artfynd.xlsx
+++ b/artfynd/A 8596-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>113084922</v>
       </c>
       <c r="B3" t="n">
-        <v>96480</v>
+        <v>96496</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8596-2022 artfynd.xlsx
+++ b/artfynd/A 8596-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>113084922</v>
       </c>
       <c r="B3" t="n">
-        <v>96496</v>
+        <v>96508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8596-2022 artfynd.xlsx
+++ b/artfynd/A 8596-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8596-2022 artfynd.xlsx
+++ b/artfynd/A 8596-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,6 +908,120 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111440583</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57353</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kvarnkullen, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>346023</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6537149</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8596-2022 artfynd.xlsx
+++ b/artfynd/A 8596-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,6 +1022,120 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114988462</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57152</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvarnkullen, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>346023</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6537149</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8596-2022 artfynd.xlsx
+++ b/artfynd/A 8596-2022 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>114988462</v>
       </c>
       <c r="B4" t="n">
-        <v>57203</v>
+        <v>57204</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8596-2022 artfynd.xlsx
+++ b/artfynd/A 8596-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80855032</v>
+        <v>114988462</v>
       </c>
       <c r="B2" t="n">
-        <v>56990</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102125</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +705,16 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346022.8787684524</v>
+        <v>346023</v>
       </c>
       <c r="R2" t="n">
-        <v>6537148.917966141</v>
+        <v>6537149</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,62 +784,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113084922</v>
+        <v>111440583</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>100090</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övre Liverud SV, Dls</t>
+          <t>Kvarnkullen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346235</v>
+        <v>346023</v>
       </c>
       <c r="R3" t="n">
-        <v>6536999</v>
+        <v>6537149</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-04</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,32 +893,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114988462</v>
+        <v>80855032</v>
       </c>
       <c r="B4" t="n">
-        <v>57206</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>102125</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,16 +923,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -992,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2019-11-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,6 +995,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113084922</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Övre Liverud SV, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>346235</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6536999</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-11-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-11-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8596-2022 artfynd.xlsx
+++ b/artfynd/A 8596-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114988462</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111440583</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855032</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,8 +1125,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113084922</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>